--- a/Result/profitability/6558.xlsx
+++ b/Result/profitability/6558.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM44"/>
+  <dimension ref="A1:AM45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6018,6 +6018,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>6558</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>290</v>
+      </c>
+      <c r="D45" t="n">
+        <v>262</v>
+      </c>
+      <c r="E45" t="n">
+        <v>29</v>
+      </c>
+      <c r="F45" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-41</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-14.19%</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="n">
+        <v>-40</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-39</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="M45" t="n">
+        <v>-0.2175</v>
+      </c>
+      <c r="N45" t="n">
+        <v>16.96625</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W45" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0.1714285714285715</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>-2.949999999999999</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>-0.2306489444878811</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0.08000000000000002</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>-0.163265306122449</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>-10.21</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>-0.5092269326683292</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK45" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
